--- a/dynamical_DE_nonfid/data/combined/cmb+dmul-w0wacdm-free.xlsx
+++ b/dynamical_DE_nonfid/data/combined/cmb+dmul-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39191618.94749684</v>
+        <v>38848789.06125671</v>
       </c>
       <c r="C2" t="n">
-        <v>-133959410.3621232</v>
+        <v>-132066553.830213</v>
       </c>
       <c r="D2" t="n">
-        <v>40460369.5202437</v>
+        <v>40190101.36931912</v>
       </c>
       <c r="E2" t="n">
-        <v>-422511.7196038837</v>
+        <v>-384456.6651680928</v>
       </c>
       <c r="F2" t="n">
-        <v>-1411155.100269691</v>
+        <v>-1410273.128538779</v>
       </c>
       <c r="G2" t="n">
-        <v>882077.9818041165</v>
+        <v>870006.9330934297</v>
       </c>
       <c r="H2" t="n">
-        <v>-2570214.440322381</v>
+        <v>-2549400.772995826</v>
       </c>
       <c r="I2" t="n">
-        <v>5871609.342357044</v>
+        <v>5812113.520747067</v>
       </c>
       <c r="J2" t="n">
-        <v>1464783.859827991</v>
+        <v>1449946.971739594</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-133959410.3195026</v>
+        <v>-132066553.8317469</v>
       </c>
       <c r="C3" t="n">
-        <v>886394347.0128779</v>
+        <v>849745426.5711586</v>
       </c>
       <c r="D3" t="n">
-        <v>-88457676.54541229</v>
+        <v>-89249646.74402802</v>
       </c>
       <c r="E3" t="n">
-        <v>15780954.12036458</v>
+        <v>14070710.03834057</v>
       </c>
       <c r="F3" t="n">
-        <v>6719463.727904072</v>
+        <v>6670152.061024725</v>
       </c>
       <c r="G3" t="n">
-        <v>-3820209.339915878</v>
+        <v>-3612896.957975636</v>
       </c>
       <c r="H3" t="n">
-        <v>7898036.095666478</v>
+        <v>7804936.894348723</v>
       </c>
       <c r="I3" t="n">
-        <v>-22891154.66366062</v>
+        <v>-22151098.53960996</v>
       </c>
       <c r="J3" t="n">
-        <v>-5687902.318393287</v>
+        <v>-5503099.419937445</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40460369.52501012</v>
+        <v>40190101.36863144</v>
       </c>
       <c r="C4" t="n">
-        <v>-88457676.60771862</v>
+        <v>-89249646.73972169</v>
       </c>
       <c r="D4" t="n">
-        <v>49054712.72150476</v>
+        <v>48630370.50813497</v>
       </c>
       <c r="E4" t="n">
-        <v>940552.8439092196</v>
+        <v>851575.4702662083</v>
       </c>
       <c r="F4" t="n">
-        <v>-1114528.149465227</v>
+        <v>-1117697.270692738</v>
       </c>
       <c r="G4" t="n">
-        <v>958505.8928931303</v>
+        <v>960069.9364309242</v>
       </c>
       <c r="H4" t="n">
-        <v>-2815817.477614185</v>
+        <v>-2797195.265144396</v>
       </c>
       <c r="I4" t="n">
-        <v>6059758.98141851</v>
+        <v>6045447.154594935</v>
       </c>
       <c r="J4" t="n">
-        <v>1514585.94761168</v>
+        <v>1511037.313190541</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-422511.7181038124</v>
+        <v>-384456.6650581583</v>
       </c>
       <c r="C5" t="n">
-        <v>15780954.11638313</v>
+        <v>14070710.03784555</v>
       </c>
       <c r="D5" t="n">
-        <v>940552.8456595109</v>
+        <v>851575.4703532154</v>
       </c>
       <c r="E5" t="n">
-        <v>980459.4396074841</v>
+        <v>828815.4155020381</v>
       </c>
       <c r="F5" t="n">
-        <v>26672.33580844275</v>
+        <v>23472.36466100222</v>
       </c>
       <c r="G5" t="n">
-        <v>-73725.21983743782</v>
+        <v>-63099.98128857268</v>
       </c>
       <c r="H5" t="n">
-        <v>-5140.3958459367</v>
+        <v>-4524.878132677684</v>
       </c>
       <c r="I5" t="n">
-        <v>-245215.0603362782</v>
+        <v>-211916.1510509882</v>
       </c>
       <c r="J5" t="n">
-        <v>-60277.02561533666</v>
+        <v>-51947.49985034655</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1411155.100493426</v>
+        <v>-1410273.128985337</v>
       </c>
       <c r="C6" t="n">
-        <v>6719463.72862951</v>
+        <v>6670152.062733593</v>
       </c>
       <c r="D6" t="n">
-        <v>-1114528.149711441</v>
+        <v>-1117697.271152479</v>
       </c>
       <c r="E6" t="n">
-        <v>26672.335813289</v>
+        <v>23472.36467798435</v>
       </c>
       <c r="F6" t="n">
-        <v>738822.3370705582</v>
+        <v>738572.9698922994</v>
       </c>
       <c r="G6" t="n">
-        <v>106171.645885567</v>
+        <v>106420.0754770136</v>
       </c>
       <c r="H6" t="n">
-        <v>41549.09656795192</v>
+        <v>41576.01648510285</v>
       </c>
       <c r="I6" t="n">
-        <v>-33877.22823620243</v>
+        <v>-33064.14761124624</v>
       </c>
       <c r="J6" t="n">
-        <v>-12098.61351831462</v>
+        <v>-11895.28305829169</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>882077.9816032439</v>
+        <v>870006.9329435553</v>
       </c>
       <c r="C7" t="n">
-        <v>-3820209.340733214</v>
+        <v>-3612896.957351922</v>
       </c>
       <c r="D7" t="n">
-        <v>958505.8925079351</v>
+        <v>960069.9363006226</v>
       </c>
       <c r="E7" t="n">
-        <v>-73725.21988495134</v>
+        <v>-63099.98128697367</v>
       </c>
       <c r="F7" t="n">
-        <v>106171.6458932307</v>
+        <v>106420.0754930676</v>
       </c>
       <c r="G7" t="n">
-        <v>66135.7023714766</v>
+        <v>64834.99750325724</v>
       </c>
       <c r="H7" t="n">
-        <v>-70691.83081232036</v>
+        <v>-70046.96464390735</v>
       </c>
       <c r="I7" t="n">
-        <v>208776.9489233606</v>
+        <v>204144.8862949521</v>
       </c>
       <c r="J7" t="n">
-        <v>52230.59014543157</v>
+        <v>51073.94565612161</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2570214.440379154</v>
+        <v>-2549400.772947626</v>
       </c>
       <c r="C8" t="n">
-        <v>7898036.098832985</v>
+        <v>7804936.894057623</v>
       </c>
       <c r="D8" t="n">
-        <v>-2815817.477343162</v>
+        <v>-2797195.265142206</v>
       </c>
       <c r="E8" t="n">
-        <v>-5140.395739729305</v>
+        <v>-4524.878126980683</v>
       </c>
       <c r="F8" t="n">
-        <v>41549.09655231033</v>
+        <v>41576.01645434169</v>
       </c>
       <c r="G8" t="n">
-        <v>-70691.83082833858</v>
+        <v>-70046.9646525086</v>
       </c>
       <c r="H8" t="n">
-        <v>177137.9929485731</v>
+        <v>175759.6683050627</v>
       </c>
       <c r="I8" t="n">
-        <v>-402918.3890480304</v>
+        <v>-399556.0682861163</v>
       </c>
       <c r="J8" t="n">
-        <v>-100316.5633745216</v>
+        <v>-99478.65393332503</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5871609.341897904</v>
+        <v>5812113.520506821</v>
       </c>
       <c r="C9" t="n">
-        <v>-22891154.6693883</v>
+        <v>-22151098.53842569</v>
       </c>
       <c r="D9" t="n">
-        <v>6059758.980106387</v>
+        <v>6045447.15446646</v>
       </c>
       <c r="E9" t="n">
-        <v>-245215.0605806941</v>
+        <v>-211916.1510612599</v>
       </c>
       <c r="F9" t="n">
-        <v>-33877.2281983811</v>
+        <v>-33064.14753382912</v>
       </c>
       <c r="G9" t="n">
-        <v>208776.9489415418</v>
+        <v>204144.886312277</v>
       </c>
       <c r="H9" t="n">
-        <v>-402918.3890062741</v>
+        <v>-399556.0682779091</v>
       </c>
       <c r="I9" t="n">
-        <v>1025421.7122715</v>
+        <v>1007726.538802075</v>
       </c>
       <c r="J9" t="n">
-        <v>255951.317726847</v>
+        <v>251534.2627219136</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1464783.859712298</v>
+        <v>1449946.971677779</v>
       </c>
       <c r="C10" t="n">
-        <v>-5687902.319819086</v>
+        <v>-5503099.419633173</v>
       </c>
       <c r="D10" t="n">
-        <v>1514585.947282973</v>
+        <v>1511037.313156796</v>
       </c>
       <c r="E10" t="n">
-        <v>-60277.02567627004</v>
+        <v>-51947.49985288167</v>
       </c>
       <c r="F10" t="n">
-        <v>-12098.6135088815</v>
+        <v>-11895.28303898461</v>
       </c>
       <c r="G10" t="n">
-        <v>52230.59014992676</v>
+        <v>51073.94566037555</v>
       </c>
       <c r="H10" t="n">
-        <v>-100316.5633640234</v>
+        <v>-99478.65393114852</v>
       </c>
       <c r="I10" t="n">
-        <v>255951.3177266501</v>
+        <v>251534.2627215901</v>
       </c>
       <c r="J10" t="n">
-        <v>64158.13755747211</v>
+        <v>63055.55057669314</v>
       </c>
     </row>
   </sheetData>

--- a/dynamical_DE_nonfid/data/combined/cmb+dmul-w0wacdm-free.xlsx
+++ b/dynamical_DE_nonfid/data/combined/cmb+dmul-w0wacdm-free.xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38848789.06125671</v>
+        <v>43586286.38603453</v>
       </c>
       <c r="C2" t="n">
-        <v>-132066553.830213</v>
+        <v>-145485252.5977808</v>
       </c>
       <c r="D2" t="n">
-        <v>40190101.36931912</v>
+        <v>45613613.86084026</v>
       </c>
       <c r="E2" t="n">
-        <v>-384456.6651680928</v>
+        <v>-471153.2062516876</v>
       </c>
       <c r="F2" t="n">
-        <v>-1410273.128538779</v>
+        <v>-1405565.212178398</v>
       </c>
       <c r="G2" t="n">
-        <v>870006.9330934297</v>
+        <v>1024106.607640557</v>
       </c>
       <c r="H2" t="n">
-        <v>-2549400.772995826</v>
+        <v>-2867466.203391369</v>
       </c>
       <c r="I2" t="n">
-        <v>5812113.520747067</v>
+        <v>6587611.569324956</v>
       </c>
       <c r="J2" t="n">
-        <v>1449946.971739594</v>
+        <v>1643221.652706971</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-132066553.8317469</v>
+        <v>-145485252.5963267</v>
       </c>
       <c r="C3" t="n">
-        <v>849745426.5711586</v>
+        <v>874570993.7735846</v>
       </c>
       <c r="D3" t="n">
-        <v>-89249646.74402802</v>
+        <v>-109022817.9455625</v>
       </c>
       <c r="E3" t="n">
-        <v>14070710.03834057</v>
+        <v>16148042.43626316</v>
       </c>
       <c r="F3" t="n">
-        <v>6670152.061024725</v>
+        <v>6591177.622027157</v>
       </c>
       <c r="G3" t="n">
-        <v>-3612896.957975636</v>
+        <v>-4328243.757881542</v>
       </c>
       <c r="H3" t="n">
-        <v>7804936.894348723</v>
+        <v>8743117.590760289</v>
       </c>
       <c r="I3" t="n">
-        <v>-22151098.53960996</v>
+        <v>-25042836.70216219</v>
       </c>
       <c r="J3" t="n">
-        <v>-5503099.419937445</v>
+        <v>-6225343.252037841</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40190101.36863144</v>
+        <v>45613613.86102451</v>
       </c>
       <c r="C4" t="n">
-        <v>-89249646.73972169</v>
+        <v>-109022817.9477248</v>
       </c>
       <c r="D4" t="n">
-        <v>48630370.50813497</v>
+        <v>54014111.48443976</v>
       </c>
       <c r="E4" t="n">
-        <v>851575.4702662083</v>
+        <v>838204.353283027</v>
       </c>
       <c r="F4" t="n">
-        <v>-1117697.270692738</v>
+        <v>-1134886.277052836</v>
       </c>
       <c r="G4" t="n">
-        <v>960069.9364309242</v>
+        <v>1111520.564005257</v>
       </c>
       <c r="H4" t="n">
-        <v>-2797195.265144396</v>
+        <v>-3151382.509692541</v>
       </c>
       <c r="I4" t="n">
-        <v>6045447.154594935</v>
+        <v>6878465.890581765</v>
       </c>
       <c r="J4" t="n">
-        <v>1511037.313190541</v>
+        <v>1718445.429354831</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-384456.6650581583</v>
+        <v>-471153.206213085</v>
       </c>
       <c r="C5" t="n">
-        <v>14070710.03784555</v>
+        <v>16148042.43615628</v>
       </c>
       <c r="D5" t="n">
-        <v>851575.4703532154</v>
+        <v>838204.3533299644</v>
       </c>
       <c r="E5" t="n">
-        <v>828815.4155020381</v>
+        <v>1059842.846585564</v>
       </c>
       <c r="F5" t="n">
-        <v>23472.36466100222</v>
+        <v>45533.39955586675</v>
       </c>
       <c r="G5" t="n">
-        <v>-63099.98128857268</v>
+        <v>-80651.06879577396</v>
       </c>
       <c r="H5" t="n">
-        <v>-4524.878132677684</v>
+        <v>-4445.692196368464</v>
       </c>
       <c r="I5" t="n">
-        <v>-211916.1510509882</v>
+        <v>-270644.8254971409</v>
       </c>
       <c r="J5" t="n">
-        <v>-51947.49985034655</v>
+        <v>-66628.90317897675</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1410273.128985337</v>
+        <v>-1405565.212187488</v>
       </c>
       <c r="C6" t="n">
-        <v>6670152.062733593</v>
+        <v>6591177.622000541</v>
       </c>
       <c r="D6" t="n">
-        <v>-1117697.271152479</v>
+        <v>-1134886.277066664</v>
       </c>
       <c r="E6" t="n">
-        <v>23472.36467798435</v>
+        <v>45533.3995533995</v>
       </c>
       <c r="F6" t="n">
-        <v>738572.9698922994</v>
+        <v>735644.4867881773</v>
       </c>
       <c r="G6" t="n">
-        <v>106420.0754770136</v>
+        <v>104840.4289318194</v>
       </c>
       <c r="H6" t="n">
-        <v>41576.01648510285</v>
+        <v>40211.82878496079</v>
       </c>
       <c r="I6" t="n">
-        <v>-33064.14761124624</v>
+        <v>-36419.96101985172</v>
       </c>
       <c r="J6" t="n">
-        <v>-11895.28305829169</v>
+        <v>-12719.75692235492</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>870006.9329435553</v>
+        <v>1024106.607636091</v>
       </c>
       <c r="C7" t="n">
-        <v>-3612896.957351922</v>
+        <v>-4328243.757927836</v>
       </c>
       <c r="D7" t="n">
-        <v>960069.9363006226</v>
+        <v>1111520.563993248</v>
       </c>
       <c r="E7" t="n">
-        <v>-63099.98128697367</v>
+        <v>-80651.06879774173</v>
       </c>
       <c r="F7" t="n">
-        <v>106420.0754930676</v>
+        <v>104840.4289316781</v>
       </c>
       <c r="G7" t="n">
-        <v>64834.99750325724</v>
+        <v>71124.10055026822</v>
       </c>
       <c r="H7" t="n">
-        <v>-70046.96464390735</v>
+        <v>-80027.3757423677</v>
       </c>
       <c r="I7" t="n">
-        <v>204144.8862949521</v>
+        <v>233290.1658050469</v>
       </c>
       <c r="J7" t="n">
-        <v>51073.94565612161</v>
+        <v>58342.13236968276</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2549400.772947626</v>
+        <v>-2867466.203393901</v>
       </c>
       <c r="C8" t="n">
-        <v>7804936.894057623</v>
+        <v>8743117.590864567</v>
       </c>
       <c r="D8" t="n">
-        <v>-2797195.265142206</v>
+        <v>-3151382.509683598</v>
       </c>
       <c r="E8" t="n">
-        <v>-4524.878126980683</v>
+        <v>-4445.692193141032</v>
       </c>
       <c r="F8" t="n">
-        <v>41576.01645434169</v>
+        <v>40211.82878433308</v>
       </c>
       <c r="G8" t="n">
-        <v>-70046.9646525086</v>
+        <v>-80027.37574280407</v>
       </c>
       <c r="H8" t="n">
-        <v>175759.6683050627</v>
+        <v>197243.5979284152</v>
       </c>
       <c r="I8" t="n">
-        <v>-399556.0682861163</v>
+        <v>-450621.8023109715</v>
       </c>
       <c r="J8" t="n">
-        <v>-99478.65393332503</v>
+        <v>-112202.3019373713</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5812113.520506821</v>
+        <v>6587611.569314955</v>
       </c>
       <c r="C9" t="n">
-        <v>-22151098.53842569</v>
+        <v>-25042836.70238263</v>
       </c>
       <c r="D9" t="n">
-        <v>6045447.15446646</v>
+        <v>6878465.890539432</v>
       </c>
       <c r="E9" t="n">
-        <v>-211916.1510612599</v>
+        <v>-270644.825504734</v>
       </c>
       <c r="F9" t="n">
-        <v>-33064.14753382912</v>
+        <v>-36419.961019372</v>
       </c>
       <c r="G9" t="n">
-        <v>204144.886312277</v>
+        <v>233290.1658053501</v>
       </c>
       <c r="H9" t="n">
-        <v>-399556.0682779091</v>
+        <v>-450621.8023097519</v>
       </c>
       <c r="I9" t="n">
-        <v>1007726.538802075</v>
+        <v>1146496.815817111</v>
       </c>
       <c r="J9" t="n">
-        <v>251534.2627219136</v>
+        <v>286128.7554029597</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1449946.971677779</v>
+        <v>1643221.652704454</v>
       </c>
       <c r="C10" t="n">
-        <v>-5503099.419633173</v>
+        <v>-6225343.252092009</v>
       </c>
       <c r="D10" t="n">
-        <v>1511037.313156796</v>
+        <v>1718445.429344376</v>
       </c>
       <c r="E10" t="n">
-        <v>-51947.49985288167</v>
+        <v>-66628.90318090524</v>
       </c>
       <c r="F10" t="n">
-        <v>-11895.28303898461</v>
+        <v>-12719.75692224775</v>
       </c>
       <c r="G10" t="n">
-        <v>51073.94566037555</v>
+        <v>58342.13236975767</v>
       </c>
       <c r="H10" t="n">
-        <v>-99478.65393114852</v>
+        <v>-112202.3019370666</v>
       </c>
       <c r="I10" t="n">
-        <v>251534.2627215901</v>
+        <v>286128.7554029613</v>
       </c>
       <c r="J10" t="n">
-        <v>63055.55057669314</v>
+        <v>71679.74889953656</v>
       </c>
     </row>
   </sheetData>
